--- a/results/tables/benchmark_smoke/benchmark_raw.xlsx
+++ b/results/tables/benchmark_smoke/benchmark_raw.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="benchmark_raw" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="benchmark_raw" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -676,16 +676,16 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>545409.0625</v>
+        <v>594868.5657086438</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01772010000422597</v>
+        <v>0.02127630007453263</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1.956992326334369e-16</v>
       </c>
       <c r="I2" t="n">
-        <v>545409.0625</v>
+        <v>594868.5657086439</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
@@ -776,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>98919.00641728763</v>
       </c>
       <c r="AO2" t="n">
         <v>267890</v>
@@ -785,13 +785,13 @@
         <v>1000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>821928.125</v>
+        <v>920847.1314172876</v>
       </c>
       <c r="AR2" t="n">
         <v>268890</v>
       </c>
       <c r="AS2" t="n">
-        <v>545409.0625</v>
+        <v>594868.5657086438</v>
       </c>
     </row>
     <row r="3">
@@ -815,16 +815,16 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>545409.0625</v>
+        <v>594868.565708575</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05980139999883249</v>
+        <v>0.06357359990943223</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>545409.0625</v>
+        <v>594868.565708575</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
@@ -908,16 +908,16 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>545409.0625</v>
+        <v>594868.5657085751</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2875901000079466</v>
+        <v>0.3831048000138253</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>545409.0625</v>
+        <v>594868.5657085751</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -997,23 +997,23 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>457449.0625</v>
+        <v>506908.5657086438</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0123745000018971</v>
+        <v>0.01300879998598248</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2.296574366704368e-16</v>
       </c>
       <c r="I5" t="n">
-        <v>457449.0625</v>
+        <v>506908.5657086439</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
@@ -1067,7 +1067,7 @@
         <v>49</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>5.820766091346741e-11</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>98919.00641728763</v>
       </c>
       <c r="AO5" t="n">
         <v>92970</v>
@@ -1106,13 +1106,13 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>821928.125</v>
+        <v>920847.1314172876</v>
       </c>
       <c r="AR5" t="n">
         <v>92970</v>
       </c>
       <c r="AS5" t="n">
-        <v>457449.0625</v>
+        <v>506908.5657086438</v>
       </c>
     </row>
     <row r="6">
@@ -1136,16 +1136,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>457449.0625</v>
+        <v>506908.565708575</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04015860000799876</v>
+        <v>0.04285490000620484</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>457449.0625</v>
+        <v>506908.565708575</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
@@ -1229,16 +1229,16 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>457449.0625</v>
+        <v>506908.5657085751</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2286251000041375</v>
+        <v>0.3109421000117436</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>457449.0625</v>
+        <v>506908.5657085751</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
